--- a/day5.xlsx
+++ b/day5.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/utkarsh/Downloads/Accio_excel/Excel-for-DA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC0C702E-32D7-5F42-8665-017FB9DA065A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1290F2F5-B90A-624F-9B37-67B318A1FA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{35B5F2F3-020D-2640-BD95-55ED81A378FB}"/>
   </bookViews>
@@ -16,7 +16,8 @@
     <sheet name="agenda" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -526,14 +527,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -548,11 +543,19 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -560,9 +563,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -678,6 +678,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -685,15 +694,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -750,40 +750,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -874,6 +840,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -881,18 +856,43 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -1090,19 +1090,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9BFC6A8B-61F5-5947-AEE6-75ABD8618E55}" name="salary_data" displayName="salary_data" ref="B5:D15" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="12" tableBorderDxfId="13" totalsRowBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9BFC6A8B-61F5-5947-AEE6-75ABD8618E55}" name="salary_data" displayName="salary_data" ref="B5:D15" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="B5:D15" xr:uid="{9BFC6A8B-61F5-5947-AEE6-75ABD8618E55}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E784B0DC-C086-0D4B-84F8-33B8391FE849}" name="STATE" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{02F1682F-C2B8-8947-97CB-8B66DCC41FC0}" name="Salary" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{84DAAFEC-30E5-2A41-A5DD-9169A890A2C0}" name="AGE" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{E784B0DC-C086-0D4B-84F8-33B8391FE849}" name="STATE" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{02F1682F-C2B8-8947-97CB-8B66DCC41FC0}" name="Salary" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{84DAAFEC-30E5-2A41-A5DD-9169A890A2C0}" name="AGE" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{630A57DB-9310-A340-A71E-C5D93B2D4DB7}" name="salary_data3" displayName="salary_data3" ref="B39:D49" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="4" tableBorderDxfId="5" totalsRowBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{630A57DB-9310-A340-A71E-C5D93B2D4DB7}" name="salary_data3" displayName="salary_data3" ref="B39:D49" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4" totalsRowBorderDxfId="3">
   <autoFilter ref="B39:D49" xr:uid="{630A57DB-9310-A340-A71E-C5D93B2D4DB7}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{6EE1BCA6-255F-BC4C-B225-EA6F0445F43F}" name="STATE" dataDxfId="2"/>
@@ -1434,80 +1434,80 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="5" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5" t="s">
+      <c r="C10" s="2"/>
+      <c r="D10" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="5"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="3"/>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="5" t="s">
+      <c r="C12" s="2"/>
+      <c r="D12" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="5" t="s">
+      <c r="C14" s="2"/>
+      <c r="D14" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="5"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="3"/>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="5" t="s">
+      <c r="C16" s="2"/>
+      <c r="D16" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
@@ -1543,90 +1543,90 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="5" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="1">
         <v>4000</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="5">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="1">
         <v>5600</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="5">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="1">
         <v>9700</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="5">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="1">
         <v>4000</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="5">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="1">
         <v>8000</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="5">
         <v>21</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="1">
         <v>9000</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="5">
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="1">
         <v>15000</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="5">
         <v>18</v>
       </c>
       <c r="I12" t="s">
@@ -1637,16 +1637,16 @@
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="1">
         <v>34000</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="5">
         <v>16</v>
       </c>
-      <c r="I13" s="17" t="s">
+      <c r="I13" t="s">
         <v>18</v>
       </c>
       <c r="K13" t="s">
@@ -1654,13 +1654,13 @@
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="1">
         <v>9000</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="5">
         <v>20</v>
       </c>
       <c r="I14" t="s">
@@ -1671,13 +1671,13 @@
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="10">
         <v>9000</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="11">
         <v>24</v>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="I30" s="17" t="s">
+      <c r="I30" t="s">
         <v>27</v>
       </c>
       <c r="K30" t="s">
@@ -1753,7 +1753,7 @@
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="I31" s="17" t="s">
+      <c r="I31" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="I33" s="17" t="s">
+      <c r="I33" t="s">
         <v>30</v>
       </c>
       <c r="K33" t="s">
@@ -1774,69 +1774,69 @@
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A35" s="14"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14"/>
-      <c r="N35" s="14"/>
-      <c r="O35" s="14"/>
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="12"/>
+      <c r="N35" s="12"/>
+      <c r="O35" s="12"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A36" s="14"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="14"/>
+      <c r="A36" s="12"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
+      <c r="O36" s="12"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="8" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="1">
         <v>4000</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="5">
         <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="1">
         <v>5600</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="5">
         <v>18</v>
       </c>
       <c r="G41" t="s">
@@ -1844,79 +1844,79 @@
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="1">
         <v>9700</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="5">
         <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="1">
         <v>4000</v>
       </c>
-      <c r="D43" s="7">
+      <c r="D43" s="5">
         <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="1">
         <v>8000</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="5">
         <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="1">
         <v>9000</v>
       </c>
-      <c r="D45" s="7">
+      <c r="D45" s="5">
         <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="1">
         <v>15000</v>
       </c>
-      <c r="D46" s="7">
+      <c r="D46" s="5">
         <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="1">
         <v>34000</v>
       </c>
-      <c r="D47" s="7">
+      <c r="D47" s="5">
         <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="1">
         <v>9000</v>
       </c>
-      <c r="D48" s="7">
+      <c r="D48" s="5">
         <v>20</v>
       </c>
       <c r="I48" t="s">
@@ -1927,16 +1927,16 @@
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="10">
         <v>9000</v>
       </c>
-      <c r="D49" s="13">
+      <c r="D49" s="11">
         <v>24</v>
       </c>
-      <c r="I49" s="17" t="s">
+      <c r="I49" t="s">
         <v>18</v>
       </c>
       <c r="K49" t="s">
@@ -1998,7 +1998,7 @@
       </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="I60" s="17" t="s">
+      <c r="I60" t="s">
         <v>27</v>
       </c>
       <c r="K60" t="s">
@@ -2006,7 +2006,7 @@
       </c>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="I61" s="17" t="s">
+      <c r="I61" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2019,7 +2019,7 @@
       </c>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="I63" s="17" t="s">
+      <c r="I63" t="s">
         <v>30</v>
       </c>
       <c r="K63" t="s">
@@ -2027,32 +2027,32 @@
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A67" s="14"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="14"/>
-      <c r="J67" s="14"/>
-      <c r="K67" s="14"/>
-      <c r="L67" s="14"/>
-      <c r="M67" s="14"/>
-      <c r="N67" s="14"/>
-      <c r="O67" s="14"/>
-      <c r="P67" s="14"/>
+      <c r="A67" s="12"/>
+      <c r="B67" s="12"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="12"/>
+      <c r="H67" s="12"/>
+      <c r="I67" s="12"/>
+      <c r="J67" s="12"/>
+      <c r="K67" s="12"/>
+      <c r="L67" s="12"/>
+      <c r="M67" s="12"/>
+      <c r="N67" s="12"/>
+      <c r="O67" s="12"/>
+      <c r="P67" s="12"/>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="C69" s="1"/>
+      <c r="C69" s="21"/>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
+      <c r="B70" s="21"/>
+      <c r="C70" s="21"/>
       <c r="E70" t="s">
         <v>51</v>
       </c>
@@ -2117,16 +2117,16 @@
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="C82" s="18" t="s">
+      <c r="C82" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="D82" s="19" t="s">
+      <c r="D82" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="E82" s="19" t="s">
+      <c r="E82" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="F82" s="20" t="s">
+      <c r="F82" s="17" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       <c r="D83">
         <v>30</v>
       </c>
-      <c r="E83" s="21">
+      <c r="E83" s="18">
         <v>0.05</v>
       </c>
       <c r="F83">
@@ -2152,11 +2152,11 @@
       <c r="D84">
         <v>100</v>
       </c>
-      <c r="E84" s="21">
+      <c r="E84" s="18">
         <v>0</v>
       </c>
       <c r="F84">
-        <f t="shared" ref="F84:F87" si="0">C84*D84*(1-E84)</f>
+        <f>C84*D84*(1-E84)</f>
         <v>400</v>
       </c>
     </row>
@@ -2167,11 +2167,11 @@
       <c r="D85">
         <v>320</v>
       </c>
-      <c r="E85" s="21">
+      <c r="E85" s="18">
         <v>0.1</v>
       </c>
       <c r="F85">
-        <f t="shared" si="0"/>
+        <f>C85*D85*(1-E85)</f>
         <v>1440</v>
       </c>
     </row>
@@ -2182,11 +2182,11 @@
       <c r="D86">
         <v>20</v>
       </c>
-      <c r="E86" s="21">
+      <c r="E86" s="18">
         <v>0.15</v>
       </c>
       <c r="F86">
-        <f t="shared" si="0"/>
+        <f>C86*D86*(1-E86)</f>
         <v>136</v>
       </c>
     </row>
@@ -2197,11 +2197,11 @@
       <c r="D87">
         <v>450</v>
       </c>
-      <c r="E87" s="21">
+      <c r="E87" s="18">
         <v>0</v>
       </c>
       <c r="F87">
-        <f t="shared" si="0"/>
+        <f>C87*D87*(1-E87)</f>
         <v>4500</v>
       </c>
     </row>
@@ -2229,34 +2229,34 @@
       </c>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A94" s="14"/>
-      <c r="B94" s="14"/>
-      <c r="C94" s="14"/>
-      <c r="D94" s="14"/>
-      <c r="E94" s="14"/>
-      <c r="F94" s="14"/>
-      <c r="G94" s="14"/>
-      <c r="H94" s="14"/>
-      <c r="I94" s="14"/>
-      <c r="J94" s="14"/>
-      <c r="K94" s="14"/>
-      <c r="L94" s="14"/>
-      <c r="M94" s="14"/>
+      <c r="A94" s="12"/>
+      <c r="B94" s="12"/>
+      <c r="C94" s="12"/>
+      <c r="D94" s="12"/>
+      <c r="E94" s="12"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
+      <c r="H94" s="12"/>
+      <c r="I94" s="12"/>
+      <c r="J94" s="12"/>
+      <c r="K94" s="12"/>
+      <c r="L94" s="12"/>
+      <c r="M94" s="12"/>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B96" s="2" t="s">
+      <c r="B96" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C96" s="1"/>
-      <c r="G96" s="21"/>
+      <c r="C96" s="21"/>
+      <c r="G96" s="18"/>
     </row>
     <row r="97" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B97" s="1"/>
-      <c r="C97" s="1"/>
-      <c r="G97" s="21"/>
+      <c r="B97" s="21"/>
+      <c r="C97" s="21"/>
+      <c r="G97" s="18"/>
     </row>
     <row r="98" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="G98" s="21"/>
+      <c r="G98" s="18"/>
     </row>
     <row r="99" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B99">
@@ -2268,7 +2268,7 @@
       <c r="F99" t="s">
         <v>59</v>
       </c>
-      <c r="G99" s="21"/>
+      <c r="G99" s="18"/>
     </row>
     <row r="100" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B100">
@@ -2282,7 +2282,7 @@
         <f>MIN(B99:B103)</f>
         <v>20</v>
       </c>
-      <c r="G100" s="21"/>
+      <c r="G100" s="18"/>
     </row>
     <row r="101" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B101">
@@ -2308,19 +2308,19 @@
       </c>
     </row>
     <row r="106" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A106" s="14"/>
-      <c r="B106" s="14"/>
-      <c r="C106" s="14"/>
-      <c r="D106" s="14"/>
-      <c r="E106" s="14"/>
-      <c r="F106" s="14"/>
-      <c r="G106" s="14"/>
-      <c r="H106" s="14"/>
-      <c r="I106" s="14"/>
-      <c r="J106" s="14"/>
-      <c r="K106" s="14"/>
-      <c r="L106" s="14"/>
-      <c r="M106" s="14"/>
+      <c r="A106" s="12"/>
+      <c r="B106" s="12"/>
+      <c r="C106" s="12"/>
+      <c r="D106" s="12"/>
+      <c r="E106" s="12"/>
+      <c r="F106" s="12"/>
+      <c r="G106" s="12"/>
+      <c r="H106" s="12"/>
+      <c r="I106" s="12"/>
+      <c r="J106" s="12"/>
+      <c r="K106" s="12"/>
+      <c r="L106" s="12"/>
+      <c r="M106" s="12"/>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B108" s="22" t="s">
@@ -2386,19 +2386,19 @@
       </c>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A117" s="14"/>
-      <c r="B117" s="14"/>
-      <c r="C117" s="14"/>
-      <c r="D117" s="14"/>
-      <c r="E117" s="14"/>
-      <c r="F117" s="14"/>
-      <c r="G117" s="14"/>
-      <c r="H117" s="14"/>
-      <c r="I117" s="14"/>
-      <c r="J117" s="14"/>
-      <c r="K117" s="14"/>
-      <c r="L117" s="14"/>
-      <c r="M117" s="14"/>
+      <c r="A117" s="12"/>
+      <c r="B117" s="12"/>
+      <c r="C117" s="12"/>
+      <c r="D117" s="12"/>
+      <c r="E117" s="12"/>
+      <c r="F117" s="12"/>
+      <c r="G117" s="12"/>
+      <c r="H117" s="12"/>
+      <c r="I117" s="12"/>
+      <c r="J117" s="12"/>
+      <c r="K117" s="12"/>
+      <c r="L117" s="12"/>
+      <c r="M117" s="12"/>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B119" s="23" t="s">
@@ -2411,7 +2411,7 @@
       <c r="C120" s="23"/>
     </row>
     <row r="122" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="C122" s="14" t="s">
+      <c r="C122" s="12" t="s">
         <v>65</v>
       </c>
       <c r="D122" t="s">
@@ -2484,29 +2484,29 @@
       </c>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A130" s="14"/>
-      <c r="B130" s="14"/>
-      <c r="C130" s="14"/>
-      <c r="D130" s="14"/>
-      <c r="E130" s="14"/>
-      <c r="F130" s="14"/>
-      <c r="G130" s="14"/>
-      <c r="H130" s="14"/>
-      <c r="I130" s="14"/>
-      <c r="J130" s="14"/>
-      <c r="K130" s="14"/>
-      <c r="L130" s="14"/>
-      <c r="M130" s="14"/>
+      <c r="A130" s="12"/>
+      <c r="B130" s="12"/>
+      <c r="C130" s="12"/>
+      <c r="D130" s="12"/>
+      <c r="E130" s="12"/>
+      <c r="F130" s="12"/>
+      <c r="G130" s="12"/>
+      <c r="H130" s="12"/>
+      <c r="I130" s="12"/>
+      <c r="J130" s="12"/>
+      <c r="K130" s="12"/>
+      <c r="L130" s="12"/>
+      <c r="M130" s="12"/>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B133" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="C133" s="1"/>
+      <c r="C133" s="21"/>
     </row>
     <row r="134" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B134" s="1"/>
-      <c r="C134" s="1"/>
+      <c r="B134" s="21"/>
+      <c r="C134" s="21"/>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.2">
       <c r="H137" t="str">
@@ -2670,33 +2670,33 @@
       </c>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A151" s="14"/>
-      <c r="B151" s="14"/>
-      <c r="C151" s="14"/>
-      <c r="D151" s="14"/>
-      <c r="E151" s="14"/>
-      <c r="F151" s="14"/>
-      <c r="G151" s="14"/>
-      <c r="H151" s="14"/>
-      <c r="I151" s="14"/>
-      <c r="J151" s="14"/>
-      <c r="K151" s="14"/>
-      <c r="L151" s="14"/>
-      <c r="M151" s="14"/>
+      <c r="A151" s="12"/>
+      <c r="B151" s="12"/>
+      <c r="C151" s="12"/>
+      <c r="D151" s="12"/>
+      <c r="E151" s="12"/>
+      <c r="F151" s="12"/>
+      <c r="G151" s="12"/>
+      <c r="H151" s="12"/>
+      <c r="I151" s="12"/>
+      <c r="J151" s="12"/>
+      <c r="K151" s="12"/>
+      <c r="L151" s="12"/>
+      <c r="M151" s="12"/>
     </row>
     <row r="153" spans="1:13" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B153" s="25" t="s">
+      <c r="B153" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="C153" s="25"/>
-      <c r="D153" s="25"/>
-      <c r="E153" s="25"/>
+      <c r="C153" s="19"/>
+      <c r="D153" s="19"/>
+      <c r="E153" s="19"/>
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="B154" s="25"/>
-      <c r="C154" s="25"/>
-      <c r="D154" s="25"/>
-      <c r="E154" s="25"/>
+      <c r="B154" s="19"/>
+      <c r="C154" s="19"/>
+      <c r="D154" s="19"/>
+      <c r="E154" s="19"/>
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C158" t="str" cm="1">
@@ -2798,12 +2798,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B153:E154"/>
     <mergeCell ref="B69:C70"/>
     <mergeCell ref="B96:C97"/>
     <mergeCell ref="B108:C109"/>
     <mergeCell ref="B119:C120"/>
     <mergeCell ref="B133:C134"/>
-    <mergeCell ref="B153:E154"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/day5.xlsx
+++ b/day5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/utkarsh/Downloads/Accio_excel/Excel-for-DA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F0DC40-3BE5-9D4F-B095-F8407A34F459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6610BEB8-AE18-F344-9EB4-6AB5323D6FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" activeTab="5" xr2:uid="{821CF553-BAE1-DA43-ABE0-2C7C8FDC2375}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" activeTab="2" xr2:uid="{821CF553-BAE1-DA43-ABE0-2C7C8FDC2375}"/>
   </bookViews>
   <sheets>
     <sheet name="agenda" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="AVERAGEIF(S)" sheetId="5" r:id="rId5"/>
     <sheet name="LARGE_SMALL" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -487,17 +487,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1417,25 +1417,25 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>45</v>
       </c>
       <c r="F8" t="s">
@@ -1443,79 +1443,79 @@
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="6">
         <v>4000</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="6">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="6">
         <v>5600</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>18</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>9700</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="6">
         <v>4000</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>20</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="6">
         <v>8000</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="6">
         <v>21</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="6">
         <v>9000</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="6">
         <v>15000</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="6">
         <v>18</v>
       </c>
       <c r="F15" t="s">
@@ -1526,13 +1526,13 @@
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="6">
         <v>34000</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="6">
         <v>16</v>
       </c>
       <c r="F16" t="s">
@@ -1543,24 +1543,24 @@
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="6">
         <v>9000</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="6">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="6">
         <v>9000</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="6">
         <v>24</v>
       </c>
     </row>
@@ -1658,38 +1658,38 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="3" spans="2:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="10"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="8"/>
     </row>
     <row r="4" spans="2:8" ht="16" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="8"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>4000</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <v>17</v>
       </c>
       <c r="F8" t="s">
@@ -1697,68 +1697,68 @@
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="6">
         <v>5600</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="6">
         <v>18</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="6">
         <v>9700</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>4000</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="6">
         <v>8000</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="6">
         <v>9000</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="6">
         <v>17</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="6">
         <v>15000</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <v>18</v>
       </c>
       <c r="F14" t="s">
@@ -1769,13 +1769,13 @@
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="6">
         <v>34000</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="6">
         <v>16</v>
       </c>
       <c r="F15" t="s">
@@ -1786,13 +1786,13 @@
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="6">
         <v>9000</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="6">
         <v>20</v>
       </c>
       <c r="F16" t="s">
@@ -1803,13 +1803,13 @@
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="6">
         <v>9000</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="6">
         <v>24</v>
       </c>
       <c r="H17" s="3"/>
@@ -1865,57 +1865,57 @@
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="6">
         <v>4000</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="6">
         <v>17</v>
       </c>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38" s="6">
         <v>5600</v>
       </c>
-      <c r="D38" s="7">
+      <c r="D38" s="6">
         <v>18</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="6">
         <v>9700</v>
       </c>
-      <c r="D39" s="7">
+      <c r="D39" s="6">
         <v>19</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="6">
         <v>4000</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="6">
         <v>20</v>
       </c>
       <c r="F40" t="s">
@@ -1923,24 +1923,24 @@
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B41" s="7" t="s">
+      <c r="B41" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="6">
         <v>8000</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="6">
         <v>21</v>
       </c>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C42" s="6">
         <v>9000</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="6">
         <v>17</v>
       </c>
       <c r="F42">
@@ -1953,46 +1953,46 @@
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B43" s="7" t="s">
+      <c r="B43" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C43" s="7">
+      <c r="C43" s="6">
         <v>15000</v>
       </c>
-      <c r="D43" s="7">
+      <c r="D43" s="6">
         <v>18</v>
       </c>
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B44" s="7" t="s">
+      <c r="B44" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="6">
         <v>34000</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="6">
         <v>16</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C45" s="7">
+      <c r="C45" s="6">
         <v>9000</v>
       </c>
-      <c r="D45" s="7">
+      <c r="D45" s="6">
         <v>20</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C46" s="7">
+      <c r="C46" s="6">
         <v>9000</v>
       </c>
-      <c r="D46" s="7">
+      <c r="D46" s="6">
         <v>24</v>
       </c>
     </row>
@@ -2022,35 +2022,35 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>4000</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>17</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>5600</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="6">
         <v>18</v>
       </c>
       <c r="F5" t="s">
@@ -2058,24 +2058,24 @@
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>9700</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="6">
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>4000</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>20</v>
       </c>
       <c r="F7">
@@ -2088,35 +2088,35 @@
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>8000</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="6">
         <v>9000</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="6">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="6">
         <v>15000</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>18</v>
       </c>
       <c r="F10" t="s">
@@ -2124,24 +2124,24 @@
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>34000</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="6">
         <v>9000</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>20</v>
       </c>
       <c r="F12">
@@ -2154,13 +2154,13 @@
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="6">
         <v>9000</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="6">
         <v>24</v>
       </c>
     </row>
@@ -2175,17 +2175,17 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
         <v>4000</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="7">
+      <c r="A3" s="6">
         <v>5600</v>
       </c>
       <c r="C3" t="s">
@@ -2193,12 +2193,12 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="7">
+      <c r="A4" s="6">
         <v>9700</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="7">
+      <c r="A5" s="6">
         <v>4000</v>
       </c>
       <c r="C5">
@@ -2211,12 +2211,12 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="7">
+      <c r="A6" s="6">
         <v>8000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="7">
+      <c r="A7" s="6">
         <v>9000</v>
       </c>
       <c r="C7" t="s">
@@ -2224,12 +2224,12 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="7">
+      <c r="A8" s="6">
         <v>15000</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="7">
+      <c r="A9" s="6">
         <v>34000</v>
       </c>
       <c r="C9" t="s">
@@ -2240,7 +2240,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="7">
+      <c r="A10" s="6">
         <v>9000</v>
       </c>
       <c r="C10" t="s">
@@ -2251,7 +2251,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="7">
+      <c r="A11" s="6">
         <v>9000</v>
       </c>
     </row>
@@ -2276,18 +2276,18 @@
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="9" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C21" s="7">
+      <c r="C21" s="6">
         <v>4000</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="10">
         <f>RANK(C21,$C$21:$C$30,1)</f>
         <v>1</v>
       </c>
@@ -2297,28 +2297,28 @@
       </c>
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C22" s="7">
+      <c r="C22" s="6">
         <v>5600</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="10">
         <f t="shared" ref="D22:D30" si="0">RANK(C22,$C$21:$C$30,1)</f>
         <v>3</v>
       </c>
     </row>
     <row r="23" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C23" s="7">
+      <c r="C23" s="6">
         <v>9700</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="10">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
     <row r="24" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C24" s="7">
+      <c r="C24" s="6">
         <v>4000</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="10">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -2327,19 +2327,19 @@
       </c>
     </row>
     <row r="25" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C25" s="7">
+      <c r="C25" s="6">
         <v>8000</v>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="10">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="26" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C26" s="7">
+      <c r="C26" s="6">
         <v>9000</v>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="10">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -2348,19 +2348,19 @@
       </c>
     </row>
     <row r="27" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C27" s="7">
+      <c r="C27" s="6">
         <v>15000</v>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="10">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
     <row r="28" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C28" s="7">
+      <c r="C28" s="6">
         <v>34000</v>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="10">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -2369,19 +2369,19 @@
       </c>
     </row>
     <row r="29" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C29" s="7">
+      <c r="C29" s="6">
         <v>9000</v>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="10">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="30" spans="3:6" x14ac:dyDescent="0.2">
-      <c r="C30" s="7">
+      <c r="C30" s="6">
         <v>9000</v>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="10">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
